--- a/data/trans_orig/P34A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36926</t>
+          <t>37708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83274</t>
+          <t>81993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24885</t>
+          <t>24488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50918</t>
+          <t>48999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100766</t>
+          <t>98417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33803</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15969</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88882</t>
+          <t>90101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127816</t>
+          <t>128310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105234</t>
+          <t>107930</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133031</t>
+          <t>134089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>204955</t>
+          <t>204892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251568</t>
+          <t>251978</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87091</t>
+          <t>86803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124532</t>
+          <t>124158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77827</t>
+          <t>78967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103761</t>
+          <t>104486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>175522</t>
+          <t>174439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220122</t>
+          <t>222967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43710</t>
+          <t>40983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43865</t>
+          <t>43485</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69869</t>
+          <t>70773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64252</t>
+          <t>65043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101114</t>
+          <t>100979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41804</t>
+          <t>41773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79130</t>
+          <t>81763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>36756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66191</t>
+          <t>65915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108540</t>
+          <t>109571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51261</t>
+          <t>55147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105452</t>
+          <t>105566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38969</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77726</t>
+          <t>75542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133698</t>
+          <t>132050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>158050</t>
+          <t>157388</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>213417</t>
+          <t>215270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>170788</t>
+          <t>170229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212193</t>
+          <t>210524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>341141</t>
+          <t>341521</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>411370</t>
+          <t>411237</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69410</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111749</t>
+          <t>109641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82986</t>
+          <t>84649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114735</t>
+          <t>114054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165214</t>
+          <t>162926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213711</t>
+          <t>214738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85099</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133196</t>
+          <t>130878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151944</t>
+          <t>153862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191369</t>
+          <t>190624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250687</t>
+          <t>250472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314079</t>
+          <t>312065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>25946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51122</t>
+          <t>49577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>43165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67787</t>
+          <t>67891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76394</t>
+          <t>75454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110201</t>
+          <t>108479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47976</t>
+          <t>46740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78819</t>
+          <t>79443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68147</t>
+          <t>67836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104968</t>
+          <t>105231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87040</t>
+          <t>85527</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>117580</t>
+          <t>117240</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117223</t>
+          <t>116939</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>148006</t>
+          <t>147133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>211919</t>
+          <t>212360</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>256396</t>
+          <t>253919</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36132</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60458</t>
+          <t>61208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51597</t>
+          <t>51515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74338</t>
+          <t>74310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94047</t>
+          <t>94060</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127725</t>
+          <t>128115</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54380</t>
+          <t>53265</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83524</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>64041</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89597</t>
+          <t>88870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125030</t>
+          <t>126026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164780</t>
+          <t>166196</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47917</t>
+          <t>45255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79225</t>
+          <t>76814</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>30942</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62554</t>
+          <t>61537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45267</t>
+          <t>45502</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51290</t>
+          <t>50529</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100272</t>
+          <t>98298</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>108748</t>
+          <t>106223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151083</t>
+          <t>150299</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>189173</t>
+          <t>189709</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>331755</t>
+          <t>333910</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>316003</t>
+          <t>314053</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>484396</t>
+          <t>470656</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62054</t>
+          <t>61384</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106222</t>
+          <t>104505</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84346</t>
+          <t>82792</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>202470</t>
+          <t>207871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>156614</t>
+          <t>159565</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>292545</t>
+          <t>288811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18460</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44029</t>
+          <t>41866</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29376</t>
+          <t>30220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66504</t>
+          <t>66792</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>54332</t>
+          <t>53773</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99756</t>
+          <t>94885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35018</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>116328</t>
+          <t>116516</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>139797</t>
+          <t>138692</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>163271</t>
+          <t>163407</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>179063</t>
+          <t>178096</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>284487</t>
+          <t>286391</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>311349</t>
+          <t>312758</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19390</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32110</t>
+          <t>31681</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>30667</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47381</t>
+          <t>46976</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>58065</t>
+          <t>60976</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>33765</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>56820</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>87163</t>
+          <t>87504</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>90346</t>
+          <t>90437</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>117522</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>109058</t>
+          <t>110100</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>134408</t>
+          <t>135092</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>207113</t>
+          <t>205794</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>245095</t>
+          <t>243855</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14154</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>86049</t>
+          <t>87141</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>115561</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>90675</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>114502</t>
+          <t>115530</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>185701</t>
+          <t>183035</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>223385</t>
+          <t>223057</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>65812</t>
+          <t>65646</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>108593</t>
+          <t>106247</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>31911</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>91714</t>
+          <t>92098</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>92100</t>
+          <t>85704</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>183546</t>
+          <t>183321</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>53738</t>
+          <t>51879</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>94496</t>
+          <t>95833</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>24528</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>77661</t>
+          <t>77882</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>80100</t>
+          <t>73551</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>158310</t>
+          <t>158204</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>263429</t>
+          <t>260515</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>321307</t>
+          <t>322575</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>335104</t>
+          <t>335428</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>655752</t>
+          <t>663740</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>624566</t>
+          <t>629151</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1024698</t>
+          <t>1040283</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>60380</t>
+          <t>60674</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>94683</t>
+          <t>93805</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>59966</t>
+          <t>60458</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>179649</t>
+          <t>180090</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>126007</t>
+          <t>122262</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>250961</t>
+          <t>249147</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>79337</t>
+          <t>79866</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>120383</t>
+          <t>119017</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>64689</t>
+          <t>63541</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>182113</t>
+          <t>182221</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>139890</t>
+          <t>143019</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>278605</t>
+          <t>278226</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>44932</t>
+          <t>44507</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>147410</t>
+          <t>146099</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>61529</t>
+          <t>61924</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>90923</t>
+          <t>92409</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>189410</t>
+          <t>191048</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>42055</t>
+          <t>39720</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>124485</t>
+          <t>125945</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>35116</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>58940</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>80928</t>
+          <t>78731</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>162813</t>
+          <t>163713</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>373231</t>
+          <t>372334</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>744420</t>
+          <t>737679</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>342854</t>
+          <t>341762</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>387832</t>
+          <t>387356</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>749078</t>
+          <t>746113</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1204723</t>
+          <t>1196617</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>84206</t>
+          <t>88808</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>259471</t>
+          <t>258954</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>193031</t>
+          <t>192661</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>233982</t>
+          <t>235587</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>237444</t>
+          <t>239128</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>473193</t>
+          <t>477259</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>45900</t>
+          <t>44317</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>32736</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>54024</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>44370</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>92138</t>
+          <t>93021</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>318403</t>
+          <t>310738</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>462396</t>
+          <t>457426</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>194492</t>
+          <t>193306</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>271469</t>
+          <t>270362</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>551010</t>
+          <t>551412</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>713080</t>
+          <t>712681</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>330344</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>474290</t>
+          <t>473739</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>177890</t>
+          <t>171489</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>249846</t>
+          <t>248403</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>546604</t>
+          <t>545513</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>706277</t>
+          <t>700575</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1403834</t>
+          <t>1400195</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2001886</t>
+          <t>2024877</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1672264</t>
+          <t>1674126</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2170552</t>
+          <t>2161076</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3116160</t>
+          <t>3120845</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3872411</t>
+          <t>3834732</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>471932</t>
+          <t>467717</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>674553</t>
+          <t>670081</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>620377</t>
+          <t>614433</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>843105</t>
+          <t>846267</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1185873</t>
+          <t>1199204</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1485947</t>
+          <t>1484528</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>366725</t>
+          <t>364188</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>520105</t>
+          <t>521798</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>514108</t>
+          <t>516866</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>689909</t>
+          <t>689143</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>949168</t>
+          <t>946127</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1187350</t>
+          <t>1183007</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>44786</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81993</t>
+          <t>62415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24488</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70437</t>
+          <t>59134</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48999</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98417</t>
+          <t>78612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>17069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42437</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107398</t>
+          <t>112231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90101</t>
+          <t>94413</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>128310</t>
+          <t>128908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120103</t>
+          <t>133093</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107930</t>
+          <t>118580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134089</t>
+          <t>148495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>227501</t>
+          <t>245323</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>204892</t>
+          <t>222192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251978</t>
+          <t>267318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>105881</t>
+          <t>102665</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86803</t>
+          <t>87317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124158</t>
+          <t>118656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91070</t>
+          <t>102474</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78967</t>
+          <t>89674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104486</t>
+          <t>115841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>196950</t>
+          <t>205139</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174439</t>
+          <t>184302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222967</t>
+          <t>226842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25759</t>
+          <t>41067</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>28957</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40983</t>
+          <t>55727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>54528</t>
+          <t>58052</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43485</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70773</t>
+          <t>70086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>80287</t>
+          <t>99118</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65043</t>
+          <t>82626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100979</t>
+          <t>118917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59137</t>
+          <t>59666</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41773</t>
+          <t>41970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>79100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36756</t>
+          <t>37286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>85751</t>
+          <t>86191</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65915</t>
+          <t>67705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109571</t>
+          <t>109886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76390</t>
+          <t>71241</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55147</t>
+          <t>52348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105566</t>
+          <t>99735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38052</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>102876</t>
+          <t>97913</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75542</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132050</t>
+          <t>126143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>185316</t>
+          <t>191401</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>157388</t>
+          <t>164600</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215270</t>
+          <t>218152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>190022</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>170229</t>
+          <t>182217</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>210524</t>
+          <t>222634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375338</t>
+          <t>394007</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>341521</t>
+          <t>361057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>411237</t>
+          <t>428796</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88319</t>
+          <t>91715</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70599</t>
+          <t>72833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109641</t>
+          <t>115737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>99056</t>
+          <t>106898</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84649</t>
+          <t>92875</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114054</t>
+          <t>125226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>187374</t>
+          <t>198613</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162926</t>
+          <t>174459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214738</t>
+          <t>225390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84313</t>
+          <t>93316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130878</t>
+          <t>137972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>172212</t>
+          <t>183195</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153862</t>
+          <t>164414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190624</t>
+          <t>202740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>279944</t>
+          <t>298395</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250472</t>
+          <t>269616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312065</t>
+          <t>334406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>529223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>529223</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>529223</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>514390</t>
+          <t>545896</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>514390</t>
+          <t>545896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>514390</t>
+          <t>545896</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1031284</t>
+          <t>1075119</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1031284</t>
+          <t>1075119</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1031284</t>
+          <t>1075119</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37266</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49577</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>54503</t>
+          <t>55444</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43165</t>
+          <t>45516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67891</t>
+          <t>70486</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>91769</t>
+          <t>91702</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75454</t>
+          <t>75651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108479</t>
+          <t>109723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>61339</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46740</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79443</t>
+          <t>77202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36266</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>86078</t>
+          <t>85643</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67836</t>
+          <t>69261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105231</t>
+          <t>105216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>101095</t>
+          <t>101083</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85527</t>
+          <t>86487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>117240</t>
+          <t>116389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>132230</t>
+          <t>134010</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>116939</t>
+          <t>119554</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>147133</t>
+          <t>150005</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>233325</t>
+          <t>235093</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>212360</t>
+          <t>216255</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>253919</t>
+          <t>257588</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48360</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61208</t>
+          <t>60173</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61944</t>
+          <t>63539</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51515</t>
+          <t>53364</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74310</t>
+          <t>75779</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>110304</t>
+          <t>110438</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94060</t>
+          <t>94424</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128115</t>
+          <t>127758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>67796</t>
+          <t>70415</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53265</t>
+          <t>58250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83156</t>
+          <t>87712</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>75906</t>
+          <t>79084</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64041</t>
+          <t>66958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88870</t>
+          <t>94324</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>143702</t>
+          <t>149499</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126026</t>
+          <t>131242</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166196</t>
+          <t>168351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>24931</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45255</t>
+          <t>56754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>18656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>55687</t>
+          <t>65787</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>47860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76814</t>
+          <t>86829</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>44764</t>
+          <t>57691</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>41324</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61537</t>
+          <t>83829</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45502</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>74188</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50529</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98298</t>
+          <t>120526</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>127996</t>
+          <t>148818</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106223</t>
+          <t>126386</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150299</t>
+          <t>176654</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>243356</t>
+          <t>197147</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>189709</t>
+          <t>178757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>333910</t>
+          <t>217836</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>371351</t>
+          <t>345965</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>314053</t>
+          <t>313494</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>470656</t>
+          <t>375502</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>79652</t>
+          <t>87945</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61384</t>
+          <t>68153</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104505</t>
+          <t>112012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>130335</t>
+          <t>108908</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82792</t>
+          <t>93476</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207871</t>
+          <t>128317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>209987</t>
+          <t>196853</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159565</t>
+          <t>172141</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>288811</t>
+          <t>230982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>28435</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>27984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41866</t>
+          <t>56241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>48037</t>
+          <t>55156</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30220</t>
+          <t>43180</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66792</t>
+          <t>70473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>76472</t>
+          <t>95490</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53773</t>
+          <t>77107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>94885</t>
+          <t>117919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>9,71%</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>311966</t>
+          <t>372488</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>311966</t>
+          <t>372488</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>311966</t>
+          <t>372488</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>787684</t>
+          <t>794450</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>787684</t>
+          <t>794450</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>787684</t>
+          <t>794450</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30988</t>
+          <t>35094</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36059</t>
+          <t>39045</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,27 +3636,27 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>29566</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>128387</t>
+          <t>148723</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>116516</t>
+          <t>136215</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>138692</t>
+          <t>160176</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>171431</t>
+          <t>186640</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>163407</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>178096</t>
+          <t>194392</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>299818</t>
+          <t>335362</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>286391</t>
+          <t>320488</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>312758</t>
+          <t>349710</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>27095</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31681</t>
+          <t>34302</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>38144</t>
+          <t>40970</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>50624</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>207897</t>
+          <t>226436</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>207897</t>
+          <t>226436</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>207897</t>
+          <t>226436</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>386639</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>386639</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>386639</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>877</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>45747</t>
+          <t>42288</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34404</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>55150</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>70628</t>
+          <t>67179</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>56820</t>
+          <t>52379</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>87504</t>
+          <t>81912</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>103286</t>
+          <t>102280</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>90437</t>
+          <t>89616</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>117522</t>
+          <t>116683</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>122280</t>
+          <t>124954</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>110100</t>
+          <t>110568</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>135092</t>
+          <t>137087</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>225566</t>
+          <t>227234</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>205794</t>
+          <t>208983</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>243855</t>
+          <t>246180</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>100379</t>
+          <t>105624</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>87141</t>
+          <t>92162</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>115776</t>
+          <t>120687</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>102671</t>
+          <t>106700</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>90675</t>
+          <t>93632</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>115530</t>
+          <t>119280</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>203050</t>
+          <t>212324</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>183035</t>
+          <t>193426</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>223057</t>
+          <t>232395</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>84085</t>
+          <t>96472</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>65646</t>
+          <t>76334</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>106247</t>
+          <t>123047</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>64286</t>
+          <t>76292</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>31911</t>
+          <t>61582</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>92098</t>
+          <t>93623</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>148371</t>
+          <t>172763</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>85704</t>
+          <t>147184</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>183321</t>
+          <t>204379</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>71307</t>
+          <t>78205</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>51879</t>
+          <t>59733</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>95833</t>
+          <t>103676</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>59252</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22057</t>
+          <t>46108</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>77882</t>
+          <t>76371</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>124577</t>
+          <t>137457</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>73551</t>
+          <t>112375</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>158204</t>
+          <t>167211</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>289444</t>
+          <t>332082</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>260515</t>
+          <t>302093</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>322575</t>
+          <t>366531</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>466409</t>
+          <t>316040</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>335428</t>
+          <t>291674</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>663740</t>
+          <t>341243</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>755853</t>
+          <t>648122</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>629151</t>
+          <t>610076</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1040283</t>
+          <t>692293</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>75873</t>
+          <t>89955</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>60674</t>
+          <t>72287</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>110923</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>129431</t>
+          <t>153775</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>60458</t>
+          <t>132852</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>180090</t>
+          <t>175379</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>205304</t>
+          <t>243730</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>122262</t>
+          <t>215192</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>249147</t>
+          <t>273002</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>98613</t>
+          <t>117532</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>79866</t>
+          <t>95571</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>119017</t>
+          <t>142347</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>131993</t>
+          <t>161092</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>63541</t>
+          <t>139854</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>182221</t>
+          <t>182761</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>230607</t>
+          <t>278624</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>143019</t>
+          <t>247842</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>278226</t>
+          <t>308760</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>619322</t>
+          <t>714245</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>619322</t>
+          <t>714245</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>619322</t>
+          <t>714245</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>845390</t>
+          <t>766451</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>845390</t>
+          <t>766451</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>845390</t>
+          <t>766451</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1464712</t>
+          <t>1480697</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1464712</t>
+          <t>1480697</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1464712</t>
+          <t>1480697</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>118315</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>98759</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>146099</t>
+          <t>145555</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>49652</t>
+          <t>55933</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>44150</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>61924</t>
+          <t>70829</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>152266</t>
+          <t>174248</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>92409</t>
+          <t>149691</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>191048</t>
+          <t>202735</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>85562</t>
+          <t>103581</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>39720</t>
+          <t>83235</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>125945</t>
+          <t>125201</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,27 +5647,27 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>44909</t>
+          <t>52747</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>35116</t>
+          <t>40866</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>58617</t>
+          <t>68094</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>130470</t>
+          <t>156328</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>78731</t>
+          <t>131259</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>163713</t>
+          <t>181637</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>525235</t>
+          <t>332785</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>372334</t>
+          <t>304166</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>737679</t>
+          <t>362270</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>364426</t>
+          <t>427687</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>341762</t>
+          <t>403178</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>387356</t>
+          <t>454576</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>889661</t>
+          <t>760472</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>746113</t>
+          <t>720951</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1196617</t>
+          <t>801420</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>183780</t>
+          <t>208479</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>88808</t>
+          <t>185151</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>258954</t>
+          <t>235625</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>212341</t>
+          <t>240609</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>192661</t>
+          <t>217285</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>235587</t>
+          <t>264033</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>396122</t>
+          <t>449088</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>239128</t>
+          <t>415917</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>477259</t>
+          <t>483447</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>29302</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>44765</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>42708</t>
+          <t>52119</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>32749</t>
+          <t>40998</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>54024</t>
+          <t>65905</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>72010</t>
+          <t>84586</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>44370</t>
+          <t>69519</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>104029</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>926493</t>
+          <t>795627</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>926493</t>
+          <t>795627</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>926493</t>
+          <t>795627</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>714036</t>
+          <t>829095</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>714036</t>
+          <t>829095</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>714036</t>
+          <t>829095</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1640529</t>
+          <t>1624722</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1640529</t>
+          <t>1624722</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1640529</t>
+          <t>1624722</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>401516</t>
+          <t>427915</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>310738</t>
+          <t>385967</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>457426</t>
+          <t>476861</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>238907</t>
+          <t>261409</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>193306</t>
+          <t>233955</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>270362</t>
+          <t>289961</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>640422</t>
+          <t>689324</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>551412</t>
+          <t>638639</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>712681</t>
+          <t>746470</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>414771</t>
+          <t>447172</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>330344</t>
+          <t>401215</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>473739</t>
+          <t>498606</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>217074</t>
+          <t>233617</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>171489</t>
+          <t>207093</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>248403</t>
+          <t>262965</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>631845</t>
+          <t>680788</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>545513</t>
+          <t>627055</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>700575</t>
+          <t>742880</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1568158</t>
+          <t>1469402</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1400195</t>
+          <t>1406597</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2024877</t>
+          <t>1531002</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1810256</t>
+          <t>1722176</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1674126</t>
+          <t>1664885</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2161076</t>
+          <t>1772304</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>3378413</t>
+          <t>3191578</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3120845</t>
+          <t>3106798</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3834732</t>
+          <t>3273976</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>603454</t>
+          <t>650676</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>467717</t>
+          <t>604745</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>670081</t>
+          <t>705451</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>755648</t>
+          <t>809626</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>614433</t>
+          <t>766475</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>846267</t>
+          <t>857682</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1359102</t>
+          <t>1460302</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1199204</t>
+          <t>1395217</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1484528</t>
+          <t>1529639</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>462648</t>
+          <t>527629</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>364188</t>
+          <t>482240</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>521798</t>
+          <t>573044</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>631364</t>
+          <t>699204</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>516866</t>
+          <t>660686</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>689143</t>
+          <t>742218</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>1094012</t>
+          <t>1226833</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>946127</t>
+          <t>1160389</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1183007</t>
+          <t>1289408</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
